--- a/derivatives/fsl/randomise/L3_model-1_task-socialdoors_type-act_cnum-4_cname-win-loss/randomise_design_n75-age.xlsx
+++ b/derivatives/fsl/randomise/L3_model-1_task-socialdoors_type-act_cnum-4_cname-win-loss/randomise_design_n75-age.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameswyngaarden/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameswyngaarden/Documents/GitHub/rf1-sra-socdoors/derivatives/fsl/randomise/L3_model-1_task-socialdoors_type-act_cnum-4_cname-win-loss/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDAE93D-8D70-D94A-B267-470DBEE6268B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B0217E-E0D3-544A-BF80-465AC980E00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7940" yWindow="1000" windowWidth="20480" windowHeight="16060" xr2:uid="{423C3340-88B7-4D47-B4F7-18EE9288C601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -468,10 +468,9 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <f>C2-$C$77</f>
         <v>19.331866666666663</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="4">
         <v>62.96</v>
       </c>
     </row>
@@ -480,10 +479,9 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <f t="shared" ref="B3:B66" si="0">C3-$C$77</f>
         <v>-11.678133333333339</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="4">
         <v>31.95</v>
       </c>
     </row>
@@ -492,10 +490,9 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <f t="shared" si="0"/>
         <v>-7.6881333333333401</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>35.94</v>
       </c>
     </row>
@@ -504,10 +501,9 @@
         <v>1</v>
       </c>
       <c r="B5" s="4">
-        <f t="shared" si="0"/>
         <v>25.011866666666663</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4">
         <v>68.64</v>
       </c>
     </row>
@@ -516,10 +512,9 @@
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <f t="shared" si="0"/>
         <v>18.411866666666661</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="4">
         <v>62.04</v>
       </c>
     </row>
@@ -528,10 +523,9 @@
         <v>1</v>
       </c>
       <c r="B7" s="4">
-        <f t="shared" si="0"/>
         <v>-15.728133333333339</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>27.9</v>
       </c>
     </row>
@@ -540,10 +534,9 @@
         <v>1</v>
       </c>
       <c r="B8" s="4">
-        <f t="shared" si="0"/>
         <v>-1.7181333333333413</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="4">
         <v>41.91</v>
       </c>
     </row>
@@ -552,10 +545,9 @@
         <v>1</v>
       </c>
       <c r="B9" s="4">
-        <f t="shared" si="0"/>
         <v>24.171866666666659</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="4">
         <v>67.8</v>
       </c>
     </row>
@@ -564,10 +556,9 @@
         <v>1</v>
       </c>
       <c r="B10" s="4">
-        <f t="shared" si="0"/>
         <v>25.531866666666659</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="4">
         <v>69.16</v>
       </c>
     </row>
@@ -576,10 +567,9 @@
         <v>1</v>
       </c>
       <c r="B11" s="4">
-        <f t="shared" si="0"/>
         <v>26.831866666666656</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="4">
         <v>70.459999999999994</v>
       </c>
     </row>
@@ -588,10 +578,9 @@
         <v>1</v>
       </c>
       <c r="B12" s="4">
-        <f t="shared" si="0"/>
         <v>4.4018666666666633</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="4">
         <v>48.03</v>
       </c>
     </row>
@@ -600,10 +589,9 @@
         <v>1</v>
       </c>
       <c r="B13" s="4">
-        <f t="shared" si="0"/>
         <v>6.0118666666666627</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="4">
         <v>49.64</v>
       </c>
     </row>
@@ -612,10 +600,9 @@
         <v>1</v>
       </c>
       <c r="B14" s="4">
-        <f t="shared" si="0"/>
         <v>19.70186666666666</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="4">
         <v>63.33</v>
       </c>
     </row>
@@ -624,10 +611,9 @@
         <v>1</v>
       </c>
       <c r="B15" s="4">
-        <f t="shared" si="0"/>
         <v>-8.7581333333333404</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="4">
         <v>34.869999999999997</v>
       </c>
     </row>
@@ -636,10 +622,9 @@
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <f t="shared" si="0"/>
         <v>12.771866666666661</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="4">
         <v>56.4</v>
       </c>
     </row>
@@ -648,10 +633,9 @@
         <v>1</v>
       </c>
       <c r="B17" s="4">
-        <f t="shared" si="0"/>
         <v>-16.358133333333338</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="4">
         <v>27.27</v>
       </c>
     </row>
@@ -660,10 +644,9 @@
         <v>1</v>
       </c>
       <c r="B18" s="4">
-        <f t="shared" si="0"/>
         <v>25.591866666666661</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="4">
         <v>69.22</v>
       </c>
     </row>
@@ -672,10 +655,9 @@
         <v>1</v>
       </c>
       <c r="B19" s="4">
-        <f t="shared" si="0"/>
         <v>-21.228133333333339</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="4">
         <v>22.4</v>
       </c>
     </row>
@@ -684,10 +666,9 @@
         <v>1</v>
       </c>
       <c r="B20" s="4">
-        <f t="shared" si="0"/>
         <v>-14.558133333333338</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="4">
         <v>29.07</v>
       </c>
     </row>
@@ -696,10 +677,9 @@
         <v>1</v>
       </c>
       <c r="B21" s="4">
-        <f t="shared" si="0"/>
         <v>29.771866666666668</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="4">
         <v>73.400000000000006</v>
       </c>
     </row>
@@ -708,10 +688,9 @@
         <v>1</v>
       </c>
       <c r="B22" s="4">
-        <f t="shared" si="0"/>
         <v>-16.818133333333339</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="4">
         <v>26.81</v>
       </c>
     </row>
@@ -720,10 +699,9 @@
         <v>1</v>
       </c>
       <c r="B23" s="4">
-        <f t="shared" si="0"/>
         <v>28.20186666666666</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="4">
         <v>71.83</v>
       </c>
     </row>
@@ -732,10 +710,9 @@
         <v>1</v>
       </c>
       <c r="B24" s="4">
-        <f t="shared" si="0"/>
         <v>-11.898133333333337</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="4">
         <v>31.73</v>
       </c>
     </row>
@@ -744,10 +721,9 @@
         <v>1</v>
       </c>
       <c r="B25" s="4">
-        <f t="shared" si="0"/>
         <v>1.0518666666666618</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="4">
         <v>44.68</v>
       </c>
     </row>
@@ -756,10 +732,9 @@
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <f t="shared" si="0"/>
         <v>-11.728133333333339</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="4">
         <v>31.9</v>
       </c>
     </row>
@@ -768,10 +743,9 @@
         <v>1</v>
       </c>
       <c r="B27" s="4">
-        <f t="shared" si="0"/>
         <v>25.781866666666659</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="4">
         <v>69.41</v>
       </c>
     </row>
@@ -780,10 +754,9 @@
         <v>1</v>
       </c>
       <c r="B28" s="4">
-        <f t="shared" si="0"/>
         <v>-19.038133333333338</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="4">
         <v>24.59</v>
       </c>
     </row>
@@ -792,10 +765,9 @@
         <v>1</v>
       </c>
       <c r="B29" s="4">
-        <f t="shared" si="0"/>
         <v>20.171866666666659</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="4">
         <v>63.8</v>
       </c>
     </row>
@@ -804,10 +776,9 @@
         <v>1</v>
       </c>
       <c r="B30" s="4">
-        <f t="shared" si="0"/>
         <v>26.421866666666659</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="4">
         <v>70.05</v>
       </c>
     </row>
@@ -816,10 +787,9 @@
         <v>1</v>
       </c>
       <c r="B31" s="4">
-        <f t="shared" si="0"/>
         <v>-22.198133333333338</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="4">
         <v>21.43</v>
       </c>
     </row>
@@ -828,10 +798,9 @@
         <v>1</v>
       </c>
       <c r="B32" s="4">
-        <f t="shared" si="0"/>
         <v>15.351866666666659</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="4">
         <v>58.98</v>
       </c>
     </row>
@@ -840,10 +809,9 @@
         <v>1</v>
       </c>
       <c r="B33" s="4">
-        <f t="shared" si="0"/>
         <v>-21.558133333333338</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="4">
         <v>22.07</v>
       </c>
     </row>
@@ -852,10 +820,9 @@
         <v>1</v>
       </c>
       <c r="B34" s="4">
-        <f t="shared" si="0"/>
         <v>-6.2581333333333404</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="4">
         <v>37.369999999999997</v>
       </c>
     </row>
@@ -864,10 +831,9 @@
         <v>1</v>
       </c>
       <c r="B35" s="4">
-        <f t="shared" si="0"/>
         <v>4.9718666666666635</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="4">
         <v>48.6</v>
       </c>
     </row>
@@ -876,10 +842,9 @@
         <v>1</v>
       </c>
       <c r="B36" s="4">
-        <f t="shared" si="0"/>
         <v>-10.428133333333335</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="4">
         <v>33.200000000000003</v>
       </c>
     </row>
@@ -888,10 +853,9 @@
         <v>1</v>
       </c>
       <c r="B37" s="4">
-        <f t="shared" si="0"/>
         <v>-10.25813333333334</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="4">
         <v>33.369999999999997</v>
       </c>
     </row>
@@ -900,10 +864,9 @@
         <v>1</v>
       </c>
       <c r="B38" s="4">
-        <f t="shared" si="0"/>
         <v>-9.1981333333333382</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="4">
         <v>34.43</v>
       </c>
     </row>
@@ -912,10 +875,9 @@
         <v>1</v>
       </c>
       <c r="B39" s="4">
-        <f t="shared" si="0"/>
         <v>12.531866666666659</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="4">
         <v>56.16</v>
       </c>
     </row>
@@ -924,10 +886,9 @@
         <v>1</v>
       </c>
       <c r="B40" s="4">
-        <f t="shared" si="0"/>
         <v>14.641866666666665</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="4">
         <v>58.27</v>
       </c>
     </row>
@@ -936,10 +897,9 @@
         <v>1</v>
       </c>
       <c r="B41" s="4">
-        <f t="shared" si="0"/>
         <v>-20.018133333333338</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="4">
         <v>23.61</v>
       </c>
     </row>
@@ -948,10 +908,9 @@
         <v>1</v>
       </c>
       <c r="B42" s="4">
-        <f t="shared" si="0"/>
         <v>-16.608133333333338</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="4">
         <v>27.02</v>
       </c>
     </row>
@@ -960,10 +919,9 @@
         <v>1</v>
       </c>
       <c r="B43" s="4">
-        <f t="shared" si="0"/>
         <v>27.901866666666663</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="4">
         <v>71.53</v>
       </c>
     </row>
@@ -972,10 +930,9 @@
         <v>1</v>
       </c>
       <c r="B44" s="4">
-        <f t="shared" si="0"/>
         <v>25.501866666666658</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="4">
         <v>69.13</v>
       </c>
     </row>
@@ -984,10 +941,9 @@
         <v>1</v>
       </c>
       <c r="B45" s="4">
-        <f t="shared" si="0"/>
         <v>-15.328133333333337</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="4">
         <v>28.3</v>
       </c>
     </row>
@@ -996,10 +952,9 @@
         <v>1</v>
       </c>
       <c r="B46" s="4">
-        <f t="shared" si="0"/>
         <v>-10.18813333333334</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="4">
         <v>33.44</v>
       </c>
     </row>
@@ -1008,10 +963,9 @@
         <v>1</v>
       </c>
       <c r="B47" s="4">
-        <f t="shared" si="0"/>
         <v>-21.928133333333339</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="4">
         <v>21.7</v>
       </c>
     </row>
@@ -1020,10 +974,9 @@
         <v>1</v>
       </c>
       <c r="B48" s="4">
-        <f t="shared" si="0"/>
         <v>-6.6981333333333382</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="4">
         <v>36.93</v>
       </c>
     </row>
@@ -1032,10 +985,9 @@
         <v>1</v>
       </c>
       <c r="B49" s="4">
-        <f t="shared" si="0"/>
         <v>-10.328133333333341</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="4">
         <v>33.299999999999997</v>
       </c>
     </row>
@@ -1044,10 +996,9 @@
         <v>1</v>
       </c>
       <c r="B50" s="4">
-        <f t="shared" si="0"/>
         <v>-18.118133333333336</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="4">
         <v>25.51</v>
       </c>
     </row>
@@ -1056,10 +1007,9 @@
         <v>1</v>
       </c>
       <c r="B51" s="4">
-        <f t="shared" si="0"/>
         <v>20.891866666666658</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="4">
         <v>64.52</v>
       </c>
     </row>
@@ -1068,10 +1018,9 @@
         <v>1</v>
       </c>
       <c r="B52" s="4">
-        <f t="shared" si="0"/>
         <v>-5.2681333333333384</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="4">
         <v>38.36</v>
       </c>
     </row>
@@ -1080,10 +1029,9 @@
         <v>1</v>
       </c>
       <c r="B53" s="4">
-        <f t="shared" si="0"/>
         <v>-6.0981333333333367</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="4">
         <v>37.53</v>
       </c>
     </row>
@@ -1092,10 +1040,9 @@
         <v>1</v>
       </c>
       <c r="B54" s="4">
-        <f t="shared" si="0"/>
         <v>7.5518666666666618</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="4">
         <v>51.18</v>
       </c>
     </row>
@@ -1104,10 +1051,9 @@
         <v>1</v>
       </c>
       <c r="B55" s="4">
-        <f t="shared" si="0"/>
         <v>17.601866666666659</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="4">
         <v>61.23</v>
       </c>
     </row>
@@ -1116,10 +1062,9 @@
         <v>1</v>
       </c>
       <c r="B56" s="4">
-        <f t="shared" si="0"/>
         <v>-3.9381333333333401</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="4">
         <v>39.69</v>
       </c>
     </row>
@@ -1128,10 +1073,9 @@
         <v>1</v>
       </c>
       <c r="B57" s="4">
-        <f t="shared" si="0"/>
         <v>-16.778133333333336</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="4">
         <v>26.85</v>
       </c>
     </row>
@@ -1140,10 +1084,9 @@
         <v>1</v>
       </c>
       <c r="B58" s="4">
-        <f t="shared" si="0"/>
         <v>-9.0981333333333367</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="4">
         <v>34.53</v>
       </c>
     </row>
@@ -1152,10 +1095,9 @@
         <v>1</v>
       </c>
       <c r="B59" s="4">
-        <f t="shared" si="0"/>
         <v>-0.93813333333334015</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="4">
         <v>42.69</v>
       </c>
     </row>
@@ -1164,10 +1106,9 @@
         <v>1</v>
       </c>
       <c r="B60" s="4">
-        <f t="shared" si="0"/>
         <v>-21.968133333333338</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="4">
         <v>21.66</v>
       </c>
     </row>
@@ -1176,10 +1117,9 @@
         <v>1</v>
       </c>
       <c r="B61" s="4">
-        <f t="shared" si="0"/>
         <v>-18.128133333333338</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="4">
         <v>25.5</v>
       </c>
     </row>
@@ -1188,10 +1128,9 @@
         <v>1</v>
       </c>
       <c r="B62" s="4">
-        <f t="shared" si="0"/>
         <v>-16.638133333333339</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="4">
         <v>26.99</v>
       </c>
     </row>
@@ -1200,10 +1139,9 @@
         <v>1</v>
       </c>
       <c r="B63" s="4">
-        <f t="shared" si="0"/>
         <v>14.421866666666659</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="4">
         <v>58.05</v>
       </c>
     </row>
@@ -1212,10 +1150,9 @@
         <v>1</v>
       </c>
       <c r="B64" s="4">
-        <f t="shared" si="0"/>
         <v>25.141866666666658</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="4">
         <v>68.77</v>
       </c>
     </row>
@@ -1224,10 +1161,9 @@
         <v>1</v>
       </c>
       <c r="B65" s="4">
-        <f t="shared" si="0"/>
         <v>-16.038133333333338</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="4">
         <v>27.59</v>
       </c>
     </row>
@@ -1236,10 +1172,9 @@
         <v>1</v>
       </c>
       <c r="B66" s="4">
-        <f t="shared" si="0"/>
         <v>-20.328133333333337</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="4">
         <v>23.3</v>
       </c>
     </row>
@@ -1248,10 +1183,9 @@
         <v>1</v>
       </c>
       <c r="B67" s="4">
-        <f t="shared" ref="B67:B76" si="1">C67-$C$77</f>
         <v>-3.3381333333333387</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="4">
         <v>40.29</v>
       </c>
     </row>
@@ -1260,10 +1194,9 @@
         <v>1</v>
       </c>
       <c r="B68" s="4">
-        <f t="shared" si="1"/>
         <v>-19.758133333333337</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="4">
         <v>23.87</v>
       </c>
     </row>
@@ -1272,10 +1205,9 @@
         <v>1</v>
       </c>
       <c r="B69" s="4">
-        <f t="shared" si="1"/>
         <v>-16.588133333333339</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="4">
         <v>27.04</v>
       </c>
     </row>
@@ -1284,10 +1216,9 @@
         <v>1</v>
       </c>
       <c r="B70" s="4">
-        <f t="shared" si="1"/>
         <v>-10.958133333333336</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="4">
         <v>32.67</v>
       </c>
     </row>
@@ -1296,10 +1227,9 @@
         <v>1</v>
       </c>
       <c r="B71" s="4">
-        <f t="shared" si="1"/>
         <v>2.4618666666666655</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="4">
         <v>46.09</v>
       </c>
     </row>
@@ -1308,10 +1238,9 @@
         <v>1</v>
       </c>
       <c r="B72" s="4">
-        <f t="shared" si="1"/>
         <v>-21.338133333333339</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="4">
         <v>22.29</v>
       </c>
     </row>
@@ -1320,10 +1249,9 @@
         <v>1</v>
       </c>
       <c r="B73" s="4">
-        <f t="shared" si="1"/>
         <v>-9.2681333333333384</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="4">
         <v>34.36</v>
       </c>
     </row>
@@ -1332,10 +1260,9 @@
         <v>1</v>
       </c>
       <c r="B74" s="4">
-        <f t="shared" si="1"/>
         <v>17.051866666666662</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="4">
         <v>60.68</v>
       </c>
     </row>
@@ -1344,10 +1271,9 @@
         <v>1</v>
       </c>
       <c r="B75" s="4">
-        <f t="shared" si="1"/>
         <v>-1.0281333333333365</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="4">
         <v>42.6</v>
       </c>
     </row>
@@ -1356,18 +1282,14 @@
         <v>1</v>
       </c>
       <c r="B76" s="4">
-        <f t="shared" si="1"/>
         <v>28.611866666666657</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="4">
         <v>72.239999999999995</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C77" s="1">
-        <f>AVERAGE(C2:C76)</f>
-        <v>43.628133333333338</v>
-      </c>
+      <c r="C77" s="1"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C78" s="1"/>
